--- a/Figure/TableS4_S6_SMESH_effects.xlsx
+++ b/Figure/TableS4_S6_SMESH_effects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wallancewei/Research/MOSIAC/Figure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A14B11C-E345-D045-B435-EA54D827A550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32794E7-F80B-4548-AB17-CF8A3454573B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54540" yWindow="600" windowWidth="39060" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supplementary table 4" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="248">
   <si>
     <t>Feature ID</t>
   </si>
@@ -327,198 +327,150 @@
     <t>Agathobacter_164119</t>
   </si>
   <si>
+    <t>Eubacterium_J</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Coprococcus_A_121497</t>
+  </si>
+  <si>
+    <t>Eubacterium_F</t>
+  </si>
+  <si>
     <t>Eubacterium_R</t>
   </si>
   <si>
+    <t>Agathobacter_164117</t>
+  </si>
+  <si>
+    <t>Prevotella</t>
+  </si>
+  <si>
+    <t>Anaerostipes</t>
+  </si>
+  <si>
     <t>Lachnospira</t>
   </si>
   <si>
     <t>Agathobaculum</t>
   </si>
   <si>
-    <t>Bariatricus</t>
+    <t>Bacteroides_H</t>
+  </si>
+  <si>
+    <t>Bilophila</t>
+  </si>
+  <si>
+    <t>Parabacteroides_B_862066</t>
+  </si>
+  <si>
+    <t>Odoribacter_865974</t>
+  </si>
+  <si>
+    <t>Butyricimonas</t>
+  </si>
+  <si>
+    <t>Escherichia_710834</t>
+  </si>
+  <si>
+    <t>Limosilactobacillus</t>
+  </si>
+  <si>
+    <t>Enterocloster</t>
+  </si>
+  <si>
+    <t>Lawsonibacter</t>
+  </si>
+  <si>
+    <t>Fimicola</t>
+  </si>
+  <si>
+    <t>Clostridium_Q_135822</t>
+  </si>
+  <si>
+    <t>Paramuribaculum</t>
+  </si>
+  <si>
+    <t>Desulfovibrio_R_446353</t>
+  </si>
+  <si>
+    <t>CAG-83</t>
+  </si>
+  <si>
+    <t>ER4</t>
+  </si>
+  <si>
+    <t>Streptococcus</t>
+  </si>
+  <si>
+    <t>Veillonella_A</t>
+  </si>
+  <si>
+    <t>Weissella_A_338544</t>
+  </si>
+  <si>
+    <t>Ligilactobacillus</t>
+  </si>
+  <si>
+    <t>Clostridium_T</t>
+  </si>
+  <si>
+    <t>Cluster-specific (C3)</t>
+  </si>
+  <si>
+    <t>Romboutsia_B</t>
+  </si>
+  <si>
+    <t>Dialister</t>
   </si>
   <si>
     <t>Phocaeicola_A_858004</t>
   </si>
   <si>
-    <t>Bilophila</t>
-  </si>
-  <si>
-    <t>Streptococcus</t>
-  </si>
-  <si>
-    <t>Pauljensenia</t>
-  </si>
-  <si>
-    <t>Parabacteroides_B_862066</t>
-  </si>
-  <si>
-    <t>Butyricimonas</t>
-  </si>
-  <si>
-    <t>Acidaminococcus</t>
+    <t>Blautia_A_141780</t>
+  </si>
+  <si>
+    <t>Erysipelatoclostridium</t>
+  </si>
+  <si>
+    <t>Parasutterella</t>
+  </si>
+  <si>
+    <t>Clostridium_AQ</t>
+  </si>
+  <si>
+    <t>Ruminococcus_B</t>
+  </si>
+  <si>
+    <t>UMGS1071</t>
+  </si>
+  <si>
+    <t>Cluster-specific (C4)</t>
+  </si>
+  <si>
+    <t>Faecalibacterium</t>
+  </si>
+  <si>
+    <t>Eubacterium_G</t>
+  </si>
+  <si>
+    <t>Fusicatenibacter</t>
+  </si>
+  <si>
+    <t>Roseburia</t>
+  </si>
+  <si>
+    <t>Evtepia</t>
+  </si>
+  <si>
+    <t>CAG-238</t>
   </si>
   <si>
     <t>Flavonifractor</t>
   </si>
   <si>
-    <t>Lactobacillus</t>
-  </si>
-  <si>
-    <t>Limosilactobacillus</t>
-  </si>
-  <si>
-    <t>Partially shared (C1|C2|C4)</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Eubacterium_J</t>
-  </si>
-  <si>
-    <t>Partially shared (C1|C3|C4)</t>
-  </si>
-  <si>
-    <t>Eubacterium_F</t>
-  </si>
-  <si>
-    <t>Coprococcus_A_121497</t>
-  </si>
-  <si>
-    <t>CAG-127</t>
-  </si>
-  <si>
-    <t>Agathobacter_164117</t>
-  </si>
-  <si>
-    <t>Dorea_A</t>
-  </si>
-  <si>
-    <t>Blautia_A_141781</t>
-  </si>
-  <si>
-    <t>Odoribacter_865974</t>
-  </si>
-  <si>
-    <t>Ruminococcus_B</t>
-  </si>
-  <si>
-    <t>Escherichia_710834</t>
-  </si>
-  <si>
-    <t>Enterocloster</t>
-  </si>
-  <si>
-    <t>Partially shared (C2|C3)</t>
-  </si>
-  <si>
-    <t>ER4</t>
-  </si>
-  <si>
-    <t>Partially shared (C2|C4)</t>
-  </si>
-  <si>
-    <t>Bacteroides_H</t>
-  </si>
-  <si>
-    <t>Partially shared (C3|C4)</t>
-  </si>
-  <si>
-    <t>Fimicola</t>
-  </si>
-  <si>
-    <t>Clostridium_Q_135822</t>
-  </si>
-  <si>
-    <t>Anaerostipes</t>
-  </si>
-  <si>
-    <t>Paramuribaculum</t>
-  </si>
-  <si>
-    <t>Desulfovibrio_R_446353</t>
-  </si>
-  <si>
-    <t>CAG-83</t>
-  </si>
-  <si>
-    <t>Veillonella_A</t>
-  </si>
-  <si>
-    <t>Intestinimonas</t>
-  </si>
-  <si>
-    <t>Rothia</t>
-  </si>
-  <si>
-    <t>Ligilactobacillus</t>
-  </si>
-  <si>
-    <t>Romboutsia_B</t>
-  </si>
-  <si>
-    <t>Cluster-specific (C3)</t>
-  </si>
-  <si>
-    <t>Dialister</t>
-  </si>
-  <si>
-    <t>Prevotella</t>
-  </si>
-  <si>
-    <t>Blautia_A_141780</t>
-  </si>
-  <si>
-    <t>Erysipelatoclostridium</t>
-  </si>
-  <si>
-    <t>Parasutterella</t>
-  </si>
-  <si>
-    <t>Clostridium_AQ</t>
-  </si>
-  <si>
-    <t>SFLA01</t>
-  </si>
-  <si>
-    <t>Cluster-specific (C4)</t>
-  </si>
-  <si>
-    <t>UMGS1071</t>
-  </si>
-  <si>
-    <t>Faecalibacterium</t>
-  </si>
-  <si>
-    <t>CAG-1427</t>
-  </si>
-  <si>
-    <t>Limivicinus</t>
-  </si>
-  <si>
-    <t>Faecousia</t>
-  </si>
-  <si>
-    <t>Onthenecus</t>
-  </si>
-  <si>
-    <t>Eubacterium_G</t>
-  </si>
-  <si>
-    <t>Lawsonibacter</t>
-  </si>
-  <si>
-    <t>Eubacterium_I</t>
-  </si>
-  <si>
-    <t>Mediterraneibacter_A_155507</t>
-  </si>
-  <si>
-    <t>Evtepia</t>
-  </si>
-  <si>
     <t>Anaerotignum_189125</t>
   </si>
   <si>
@@ -810,20 +762,17 @@
     <t>s_Hungatella_hathewayi</t>
   </si>
   <si>
-    <t>Supplementary Table S4. SMESH-PALM cluster-level effect estimates, pan-disease meta-analysis (GMrepo; 12 diseases, 32 datasets, 244 species; G = 2).</t>
-  </si>
-  <si>
-    <t>Supplementary Table S5. SMESH-PALM cluster-level effect estimates, pan-tumor meta-analysis (HGMT; 15 tumour types, 36 datasets, 159 genera; G = 4).</t>
-  </si>
-  <si>
-    <t>Supplementary Table S6. SMESH-PALM cluster-level effect estimates, colorectal neoplasia meta-analysis (26 study × stage strata, 2,679 samples, 260 species; G = 2).</t>
+    <t>Subset-shared (C2|C3)</t>
+  </si>
+  <si>
+    <t>Subset-shared (C3|C4)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -836,15 +785,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -867,10 +807,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1167,652 +1106,661 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="43.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
     <col min="3" max="4" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>262</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>-0.73209999999999997</v>
+      </c>
+      <c r="D2">
+        <v>-0.73209999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3">
-        <v>-0.73209999999999997</v>
+        <v>-0.41420000000000001</v>
       </c>
       <c r="D3">
-        <v>-0.73209999999999997</v>
+        <v>-0.83379999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-0.41420000000000001</v>
+        <v>-0.60709999999999997</v>
       </c>
       <c r="D4">
-        <v>-0.83379999999999999</v>
+        <v>-0.60709999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-0.60709999999999997</v>
+        <v>-0.30859999999999999</v>
       </c>
       <c r="D5">
-        <v>-0.60709999999999997</v>
+        <v>-0.88880000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6">
-        <v>-0.30859999999999999</v>
+        <v>-0.59840000000000004</v>
       </c>
       <c r="D6">
-        <v>-0.88880000000000003</v>
+        <v>-0.59840000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-0.59840000000000004</v>
+        <v>-0.2883</v>
       </c>
       <c r="D7">
-        <v>-0.59840000000000004</v>
+        <v>-0.77529999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-0.2883</v>
+        <v>-0.52849999999999997</v>
       </c>
       <c r="D8">
-        <v>-0.77529999999999999</v>
+        <v>-0.52849999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9">
-        <v>-0.52849999999999997</v>
+        <v>-0.23380000000000001</v>
       </c>
       <c r="D9">
-        <v>-0.52849999999999997</v>
+        <v>-0.8155</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-0.23380000000000001</v>
+        <v>-0.31719999999999998</v>
       </c>
       <c r="D10">
-        <v>-0.8155</v>
+        <v>-0.67310000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11">
-        <v>-0.31719999999999998</v>
+        <v>-0.48359999999999997</v>
       </c>
       <c r="D11">
-        <v>-0.67310000000000003</v>
+        <v>-0.48359999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-0.48359999999999997</v>
+        <v>-0.47739999999999999</v>
       </c>
       <c r="D12">
-        <v>-0.48359999999999997</v>
+        <v>-0.47739999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13">
-        <v>-0.47739999999999999</v>
+        <v>-0.2782</v>
       </c>
       <c r="D13">
-        <v>-0.47739999999999999</v>
+        <v>-0.63680000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-0.2782</v>
+        <v>-0.40820000000000001</v>
       </c>
       <c r="D14">
-        <v>-0.63680000000000003</v>
+        <v>-0.40820000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15">
-        <v>-0.40820000000000001</v>
+        <v>-0.4073</v>
       </c>
       <c r="D15">
-        <v>-0.40820000000000001</v>
+        <v>-0.4073</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16">
-        <v>-0.4073</v>
+        <v>-0.40029999999999999</v>
       </c>
       <c r="D16">
-        <v>-0.4073</v>
+        <v>-0.40029999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-0.40029999999999999</v>
+        <v>-0.27910000000000001</v>
       </c>
       <c r="D17">
-        <v>-0.40029999999999999</v>
+        <v>-0.50509999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
       </c>
       <c r="C18">
-        <v>-0.27910000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="D18">
-        <v>-0.50509999999999999</v>
+        <v>-0.53010000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
       </c>
       <c r="C19">
-        <v>-0.19</v>
+        <v>-0.21740000000000001</v>
       </c>
       <c r="D19">
-        <v>-0.53010000000000002</v>
+        <v>-0.4884</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-0.21740000000000001</v>
+        <v>-0.3528</v>
       </c>
       <c r="D20">
-        <v>-0.4884</v>
+        <v>-0.3528</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
       </c>
       <c r="C21">
-        <v>-0.3528</v>
+        <v>-0.34720000000000001</v>
       </c>
       <c r="D21">
-        <v>-0.3528</v>
+        <v>-0.34720000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22">
-        <v>-0.34720000000000001</v>
+        <v>-0.19389999999999999</v>
       </c>
       <c r="D22">
-        <v>-0.34720000000000001</v>
+        <v>-0.48120000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-0.19389999999999999</v>
+        <v>-0.32729999999999998</v>
       </c>
       <c r="D23">
-        <v>-0.48120000000000002</v>
+        <v>-0.32729999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24">
-        <v>-0.32729999999999998</v>
+        <v>-0.3246</v>
       </c>
       <c r="D24">
-        <v>-0.32729999999999998</v>
+        <v>-0.3246</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25">
-        <v>-0.3246</v>
+        <v>-0.32279999999999998</v>
       </c>
       <c r="D25">
-        <v>-0.3246</v>
+        <v>-0.32279999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26">
-        <v>-0.32279999999999998</v>
+        <v>-0.31819999999999998</v>
       </c>
       <c r="D26">
-        <v>-0.32279999999999998</v>
+        <v>-0.31819999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27">
-        <v>-0.31819999999999998</v>
+        <v>-0.30609999999999998</v>
       </c>
       <c r="D27">
-        <v>-0.31819999999999998</v>
+        <v>-0.30609999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-0.30609999999999998</v>
+        <v>-0.30420000000000003</v>
       </c>
       <c r="D28">
-        <v>-0.30609999999999998</v>
+        <v>-0.30420000000000003</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29">
-        <v>-0.30420000000000003</v>
+        <v>-0.30180000000000001</v>
       </c>
       <c r="D29">
-        <v>-0.30420000000000003</v>
+        <v>-0.30180000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
       </c>
       <c r="C30">
-        <v>-0.30180000000000001</v>
+        <v>-0.29949999999999999</v>
       </c>
       <c r="D30">
-        <v>-0.30180000000000001</v>
+        <v>-0.29949999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
         <v>5</v>
       </c>
       <c r="C31">
-        <v>-0.29949999999999999</v>
+        <v>-0.2989</v>
       </c>
       <c r="D31">
-        <v>-0.29949999999999999</v>
+        <v>-0.2989</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32">
-        <v>-0.2989</v>
+        <v>-0.29020000000000001</v>
       </c>
       <c r="D32">
-        <v>-0.2989</v>
+        <v>-0.29020000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
       </c>
       <c r="C33">
-        <v>-0.29020000000000001</v>
+        <v>-0.28810000000000002</v>
       </c>
       <c r="D33">
-        <v>-0.29020000000000001</v>
+        <v>-0.28810000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-0.28810000000000002</v>
+        <v>-0.28789999999999999</v>
       </c>
       <c r="D34">
-        <v>-0.28810000000000002</v>
+        <v>-0.28789999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
         <v>5</v>
       </c>
       <c r="C35">
-        <v>-0.28789999999999999</v>
+        <v>-0.28649999999999998</v>
       </c>
       <c r="D35">
-        <v>-0.28789999999999999</v>
+        <v>-0.28649999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>5</v>
       </c>
       <c r="C36">
-        <v>-0.28649999999999998</v>
+        <v>-0.28220000000000001</v>
       </c>
       <c r="D36">
-        <v>-0.28649999999999998</v>
+        <v>-0.28220000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>5</v>
       </c>
       <c r="C37">
-        <v>-0.28220000000000001</v>
+        <v>-0.28170000000000001</v>
       </c>
       <c r="D37">
-        <v>-0.28220000000000001</v>
+        <v>-0.28170000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
         <v>5</v>
       </c>
       <c r="C38">
-        <v>-0.28170000000000001</v>
+        <v>-0.27939999999999998</v>
       </c>
       <c r="D38">
-        <v>-0.28170000000000001</v>
+        <v>-0.27939999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
         <v>5</v>
       </c>
       <c r="C39">
-        <v>-0.27939999999999998</v>
+        <v>-0.2727</v>
       </c>
       <c r="D39">
-        <v>-0.27939999999999998</v>
+        <v>-0.2727</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
         <v>5</v>
       </c>
       <c r="C40">
-        <v>-0.2727</v>
+        <v>-0.26779999999999998</v>
       </c>
       <c r="D40">
-        <v>-0.2727</v>
+        <v>-0.26779999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41">
-        <v>-0.26779999999999998</v>
+        <v>-0.21829999999999999</v>
       </c>
       <c r="D41">
-        <v>-0.26779999999999998</v>
+        <v>-0.21829999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
       </c>
       <c r="C42">
-        <v>-0.21829999999999999</v>
+        <v>0.59589999999999999</v>
       </c>
       <c r="D42">
-        <v>-0.21829999999999999</v>
+        <v>0.59589999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
       </c>
       <c r="C43">
-        <v>0.59589999999999999</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="D43">
-        <v>0.59589999999999999</v>
+        <v>0.83099999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
       </c>
       <c r="C44">
-        <v>0.49099999999999999</v>
+        <v>0.67789999999999995</v>
       </c>
       <c r="D44">
-        <v>0.83099999999999996</v>
+        <v>0.67789999999999995</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
       </c>
       <c r="C45">
-        <v>0.67789999999999995</v>
+        <v>0.68559999999999999</v>
       </c>
       <c r="D45">
-        <v>0.67789999999999995</v>
+        <v>0.68559999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C46">
-        <v>0.68559999999999999</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0.68559999999999999</v>
+        <v>-1.0875999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
@@ -1821,12 +1769,12 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>-1.0875999999999999</v>
+        <v>-1.026</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
         <v>50</v>
@@ -1835,12 +1783,12 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>-1.026</v>
+        <v>-0.99350000000000005</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
         <v>50</v>
@@ -1849,12 +1797,12 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>-0.99350000000000005</v>
+        <v>-0.96199999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B50" t="s">
         <v>50</v>
@@ -1863,12 +1811,12 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>-0.96199999999999997</v>
+        <v>-0.92810000000000004</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B51" t="s">
         <v>50</v>
@@ -1877,12 +1825,12 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>-0.92810000000000004</v>
+        <v>-0.80230000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B52" t="s">
         <v>50</v>
@@ -1891,12 +1839,12 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>-0.80230000000000001</v>
+        <v>-0.79449999999999998</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B53" t="s">
         <v>50</v>
@@ -1905,12 +1853,12 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>-0.79449999999999998</v>
+        <v>-0.75760000000000005</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54" t="s">
         <v>50</v>
@@ -1919,12 +1867,12 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>-0.75760000000000005</v>
+        <v>-0.7268</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B55" t="s">
         <v>50</v>
@@ -1933,12 +1881,12 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>-0.7268</v>
+        <v>-0.70330000000000004</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
         <v>50</v>
@@ -1947,12 +1895,12 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>-0.70330000000000004</v>
+        <v>-0.68179999999999996</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B57" t="s">
         <v>50</v>
@@ -1961,12 +1909,12 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>-0.68179999999999996</v>
+        <v>-0.66269999999999996</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B58" t="s">
         <v>50</v>
@@ -1975,12 +1923,12 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>-0.66269999999999996</v>
+        <v>-0.61960000000000004</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
         <v>50</v>
@@ -1989,12 +1937,12 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>-0.61960000000000004</v>
+        <v>-0.61850000000000005</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B60" t="s">
         <v>50</v>
@@ -2003,12 +1951,12 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>-0.61850000000000005</v>
+        <v>-0.61529999999999996</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B61" t="s">
         <v>50</v>
@@ -2017,12 +1965,12 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>-0.61529999999999996</v>
+        <v>-0.56730000000000003</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
         <v>50</v>
@@ -2031,12 +1979,12 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>-0.56730000000000003</v>
+        <v>-0.54059999999999997</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B63" t="s">
         <v>50</v>
@@ -2045,12 +1993,12 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>-0.54059999999999997</v>
+        <v>-0.48630000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B64" t="s">
         <v>50</v>
@@ -2059,12 +2007,12 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>-0.48630000000000001</v>
+        <v>-0.43340000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B65" t="s">
         <v>50</v>
@@ -2073,12 +2021,12 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>-0.43340000000000001</v>
+        <v>-0.375</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B66" t="s">
         <v>50</v>
@@ -2087,12 +2035,12 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>-0.375</v>
+        <v>0.27739999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B67" t="s">
         <v>50</v>
@@ -2101,12 +2049,12 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0.27739999999999998</v>
+        <v>0.30159999999999998</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B68" t="s">
         <v>50</v>
@@ -2115,12 +2063,12 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0.30159999999999998</v>
+        <v>0.30599999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B69" t="s">
         <v>50</v>
@@ -2129,12 +2077,12 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0.30599999999999999</v>
+        <v>0.44359999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
         <v>50</v>
@@ -2143,12 +2091,12 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0.44359999999999999</v>
+        <v>0.45789999999999997</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B71" t="s">
         <v>50</v>
@@ -2157,12 +2105,12 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0.45789999999999997</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B72" t="s">
         <v>50</v>
@@ -2171,12 +2119,12 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0.46</v>
+        <v>0.46189999999999998</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B73" t="s">
         <v>50</v>
@@ -2185,12 +2133,12 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.46189999999999998</v>
+        <v>0.50390000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B74" t="s">
         <v>50</v>
@@ -2199,12 +2147,12 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0.50390000000000001</v>
+        <v>0.51270000000000004</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B75" t="s">
         <v>50</v>
@@ -2213,12 +2161,12 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0.51270000000000004</v>
+        <v>0.51749999999999996</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B76" t="s">
         <v>50</v>
@@ -2227,12 +2175,12 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0.51749999999999996</v>
+        <v>0.52600000000000002</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
         <v>50</v>
@@ -2241,12 +2189,12 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0.52600000000000002</v>
+        <v>0.53849999999999998</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s">
         <v>50</v>
@@ -2255,12 +2203,12 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>0.53849999999999998</v>
+        <v>0.5595</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
         <v>50</v>
@@ -2269,12 +2217,12 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0.5595</v>
+        <v>0.59430000000000005</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B80" t="s">
         <v>50</v>
@@ -2283,12 +2231,12 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>0.59430000000000005</v>
+        <v>0.60580000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
         <v>50</v>
@@ -2297,12 +2245,12 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.60580000000000001</v>
+        <v>0.61109999999999998</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B82" t="s">
         <v>50</v>
@@ -2311,12 +2259,12 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0.61109999999999998</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
         <v>50</v>
@@ -2325,12 +2273,12 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>0.625</v>
+        <v>0.62560000000000004</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
         <v>50</v>
@@ -2339,12 +2287,12 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.62560000000000004</v>
+        <v>0.63119999999999998</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
         <v>50</v>
@@ -2353,12 +2301,12 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>0.63119999999999998</v>
+        <v>0.63470000000000004</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
         <v>50</v>
@@ -2367,12 +2315,12 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.63470000000000004</v>
+        <v>0.64639999999999997</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B87" t="s">
         <v>50</v>
@@ -2381,12 +2329,12 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0.64639999999999997</v>
+        <v>0.65739999999999998</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
         <v>50</v>
@@ -2395,12 +2343,12 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>0.65739999999999998</v>
+        <v>0.66990000000000005</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B89" t="s">
         <v>50</v>
@@ -2409,12 +2357,12 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0.66990000000000005</v>
+        <v>0.70169999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B90" t="s">
         <v>50</v>
@@ -2423,12 +2371,12 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.70169999999999999</v>
+        <v>0.7198</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B91" t="s">
         <v>50</v>
@@ -2437,12 +2385,12 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.7198</v>
+        <v>0.7913</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B92" t="s">
         <v>50</v>
@@ -2451,12 +2399,12 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.7913</v>
+        <v>0.79930000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B93" t="s">
         <v>50</v>
@@ -2465,20 +2413,6 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0.79930000000000001</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>97</v>
-      </c>
-      <c r="B94" t="s">
-        <v>50</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-      <c r="D94">
         <v>0.92779999999999996</v>
       </c>
     </row>
@@ -2490,337 +2424,351 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>263</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>99</v>
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>-0.51839999999999997</v>
+      </c>
+      <c r="D2">
+        <v>-0.51839999999999997</v>
+      </c>
+      <c r="E2">
+        <v>-0.51839999999999997</v>
+      </c>
+      <c r="F2">
+        <v>-0.51839999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3">
-        <v>-0.26450000000000001</v>
-      </c>
-      <c r="D3">
-        <v>-0.36809999999999998</v>
+        <v>-0.4788</v>
+      </c>
+      <c r="D3" t="s">
+        <v>102</v>
       </c>
       <c r="E3">
-        <v>-0.26450000000000001</v>
+        <v>-0.4788</v>
       </c>
       <c r="F3">
-        <v>-0.26450000000000001</v>
+        <v>-0.4788</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-0.19750000000000001</v>
-      </c>
-      <c r="D4">
-        <v>-0.19750000000000001</v>
+        <v>-0.39710000000000001</v>
+      </c>
+      <c r="D4" t="s">
+        <v>102</v>
       </c>
       <c r="E4">
-        <v>-0.19750000000000001</v>
+        <v>-0.39710000000000001</v>
       </c>
       <c r="F4">
-        <v>-0.19750000000000001</v>
+        <v>-0.39710000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>-0.36359999999999998</v>
+      </c>
+      <c r="D5" t="s">
         <v>102</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>-0.15090000000000001</v>
-      </c>
-      <c r="D5">
-        <v>-0.15090000000000001</v>
-      </c>
       <c r="E5">
-        <v>-0.15090000000000001</v>
+        <v>-0.36359999999999998</v>
       </c>
       <c r="F5">
-        <v>-0.15090000000000001</v>
+        <v>-0.36359999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6">
-        <v>-0.1154</v>
+        <v>-0.23569999999999999</v>
       </c>
       <c r="D6">
-        <v>-0.1154</v>
+        <v>-0.23569999999999999</v>
       </c>
       <c r="E6">
-        <v>-0.1154</v>
+        <v>-0.23569999999999999</v>
       </c>
       <c r="F6">
-        <v>-0.1154</v>
+        <v>-0.23569999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-0.16009999999999999</v>
-      </c>
-      <c r="D7">
-        <v>-0.16009999999999999</v>
+        <v>-0.27039999999999997</v>
+      </c>
+      <c r="D7" t="s">
+        <v>102</v>
       </c>
       <c r="E7">
-        <v>-0.16009999999999999</v>
+        <v>-0.27039999999999997</v>
       </c>
       <c r="F7">
-        <v>0.16919999999999999</v>
+        <v>-0.27039999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8">
-        <v>9.0899999999999995E-2</v>
+        <v>-0.17369999999999999</v>
       </c>
       <c r="D8">
-        <v>9.0899999999999995E-2</v>
+        <v>-0.17369999999999999</v>
       </c>
       <c r="E8">
-        <v>0.25690000000000002</v>
+        <v>-0.28649999999999998</v>
       </c>
       <c r="F8">
-        <v>9.0899999999999995E-2</v>
+        <v>-0.17369999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9">
-        <v>0.17299999999999999</v>
+        <v>-0.19350000000000001</v>
       </c>
       <c r="D9">
-        <v>0.17299999999999999</v>
+        <v>-0.19350000000000001</v>
       </c>
       <c r="E9">
-        <v>0.17299999999999999</v>
+        <v>-0.19350000000000001</v>
       </c>
       <c r="F9">
-        <v>0.17299999999999999</v>
+        <v>-0.19350000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
       <c r="C10">
-        <v>0.18959999999999999</v>
+        <v>-0.11749999999999999</v>
       </c>
       <c r="D10">
-        <v>0.44180000000000003</v>
+        <v>-0.27810000000000001</v>
       </c>
       <c r="E10">
-        <v>0.18959999999999999</v>
+        <v>-0.11749999999999999</v>
       </c>
       <c r="F10">
-        <v>0.18959999999999999</v>
+        <v>-0.23569999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11">
-        <v>0.26029999999999998</v>
+        <v>-0.1119</v>
       </c>
       <c r="D11">
-        <v>0.26029999999999998</v>
+        <v>-0.1119</v>
       </c>
       <c r="E11">
-        <v>0.26029999999999998</v>
+        <v>-0.1119</v>
       </c>
       <c r="F11">
-        <v>0.26029999999999998</v>
+        <v>-0.21870000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12">
-        <v>0.2631</v>
+        <v>0.10340000000000001</v>
       </c>
       <c r="D12">
-        <v>0.2631</v>
+        <v>0.10340000000000001</v>
       </c>
       <c r="E12">
-        <v>0.2631</v>
+        <v>0.32719999999999999</v>
       </c>
       <c r="F12">
-        <v>0.2631</v>
+        <v>0.10340000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13">
-        <v>0.2984</v>
+        <v>0.1956</v>
       </c>
       <c r="D13">
-        <v>0.2984</v>
+        <v>0.1956</v>
       </c>
       <c r="E13">
-        <v>0.2984</v>
+        <v>0.1956</v>
       </c>
       <c r="F13">
-        <v>0.2984</v>
+        <v>0.1956</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14">
-        <v>0.37559999999999999</v>
+        <v>0.2009</v>
       </c>
       <c r="D14">
-        <v>0.37559999999999999</v>
+        <v>0.2009</v>
       </c>
       <c r="E14">
-        <v>0.37559999999999999</v>
+        <v>0.2009</v>
       </c>
       <c r="F14">
-        <v>0.37559999999999999</v>
+        <v>0.2009</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15">
-        <v>0.4042</v>
-      </c>
-      <c r="D15">
-        <v>0.4042</v>
+        <v>0.20649999999999999</v>
+      </c>
+      <c r="D15" t="s">
+        <v>102</v>
       </c>
       <c r="E15">
-        <v>0.4042</v>
+        <v>0.20649999999999999</v>
       </c>
       <c r="F15">
-        <v>0.4042</v>
+        <v>0.43059999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16">
-        <v>0.56920000000000004</v>
+        <v>0.3463</v>
       </c>
       <c r="D16">
-        <v>0.56920000000000004</v>
+        <v>0.3463</v>
       </c>
       <c r="E16">
-        <v>0.56920000000000004</v>
+        <v>0.3463</v>
       </c>
       <c r="F16">
-        <v>0.56920000000000004</v>
+        <v>0.3463</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>0.57769999999999999</v>
-      </c>
-      <c r="D17">
-        <v>0.57769999999999999</v>
-      </c>
-      <c r="E17" t="s">
-        <v>116</v>
+        <v>0.60529999999999995</v>
+      </c>
+      <c r="D17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17">
+        <v>0.60529999999999995</v>
       </c>
       <c r="F17">
-        <v>0.57769999999999999</v>
+        <v>0.60529999999999995</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -2828,216 +2776,216 @@
         <v>117</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>-0.4798</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18">
-        <v>-0.4798</v>
+        <v>0.71909999999999996</v>
+      </c>
+      <c r="D18">
+        <v>0.71909999999999996</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
       </c>
       <c r="F18">
-        <v>-0.4798</v>
+        <v>0.71909999999999996</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>246</v>
       </c>
       <c r="C19">
-        <v>-0.37930000000000003</v>
-      </c>
-      <c r="D19" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0.32340000000000002</v>
       </c>
       <c r="E19">
-        <v>-0.37930000000000003</v>
+        <v>0.48830000000000001</v>
       </c>
       <c r="F19">
-        <v>-0.37930000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="C20">
-        <v>-0.3125</v>
-      </c>
-      <c r="D20" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.41789999999999999</v>
+        <v>0.1724</v>
       </c>
       <c r="F20">
-        <v>-0.3125</v>
+        <v>0.2039</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C21">
-        <v>-0.3332</v>
-      </c>
-      <c r="D21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21">
-        <v>-0.3332</v>
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>-0.4002</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
       </c>
       <c r="F21">
-        <v>-0.3332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C22">
-        <v>-0.1376</v>
-      </c>
-      <c r="D22" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>-0.23080000000000001</v>
       </c>
       <c r="E22">
-        <v>-0.1376</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>-0.1376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C23">
-        <v>-0.1042</v>
-      </c>
-      <c r="D23" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0.17979999999999999</v>
       </c>
       <c r="E23">
-        <v>-0.1042</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>0.1263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C24">
-        <v>0.1386</v>
-      </c>
-      <c r="D24" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0.21629999999999999</v>
       </c>
       <c r="E24">
-        <v>0.1386</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0.1386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C25">
-        <v>0.28470000000000001</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0.2172</v>
       </c>
       <c r="E25">
-        <v>0.28470000000000001</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>0.28470000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C26">
-        <v>0.3533</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0.26640000000000003</v>
       </c>
       <c r="E26">
-        <v>0.70589999999999997</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>0.3533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C27">
-        <v>0.90510000000000002</v>
-      </c>
-      <c r="D27" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0.30690000000000001</v>
       </c>
       <c r="E27">
-        <v>0.90510000000000002</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>0.5302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0.32840000000000003</v>
+        <v>0.38159999999999999</v>
       </c>
       <c r="E28">
-        <v>0.41210000000000002</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -3045,59 +2993,59 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0.26579999999999998</v>
+        <v>0.45050000000000001</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>-0.16320000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B30" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.52829999999999999</v>
       </c>
       <c r="E30">
-        <v>0.23169999999999999</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>0.15229999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>-0.39140000000000003</v>
-      </c>
-      <c r="E31" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>-0.30459999999999998</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -3105,19 +3053,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
-      <c r="D32">
-        <v>-0.2235</v>
+      <c r="D32" t="s">
+        <v>102</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>-0.27979999999999999</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -3125,19 +3073,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
-      <c r="D33">
-        <v>-0.17799999999999999</v>
+      <c r="D33" t="s">
+        <v>102</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>-0.21510000000000001</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3145,19 +3093,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0.1807</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>0.2296</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -3165,19 +3113,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0.21629999999999999</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.2576</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3185,19 +3133,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0.2172</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>0.29959999999999998</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -3205,19 +3153,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
-      <c r="D37">
-        <v>0.37919999999999998</v>
+      <c r="D37" t="s">
+        <v>102</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.33069999999999999</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -3225,19 +3173,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0.39119999999999999</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>0.51490000000000002</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3245,19 +3193,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
-      <c r="D39">
-        <v>0.49170000000000003</v>
+      <c r="D39" t="s">
+        <v>102</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.57230000000000003</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -3265,50 +3213,50 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0.52380000000000004</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>-0.33839999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
-      <c r="D41" t="s">
-        <v>116</v>
+      <c r="D41">
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>-0.33200000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -3317,78 +3265,78 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>-0.1668</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>-0.23130000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
-      <c r="D43">
-        <v>0</v>
+      <c r="D43" t="s">
+        <v>102</v>
       </c>
       <c r="E43">
-        <v>-0.1462</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>-0.1835</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
-      <c r="D44">
-        <v>0</v>
+      <c r="D44" t="s">
+        <v>102</v>
       </c>
       <c r="E44">
-        <v>0.21940000000000001</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>-0.18260000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B45" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
-      <c r="D45">
-        <v>0</v>
+      <c r="D45" t="s">
+        <v>102</v>
       </c>
       <c r="E45">
-        <v>0.25509999999999999</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>0.31940000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -3397,18 +3345,18 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0.2828</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>0.32090000000000002</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -3417,18 +3365,18 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0.43430000000000002</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>0.49209999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -3440,15 +3388,15 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>-0.40100000000000002</v>
+        <v>0.68010000000000004</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -3456,19 +3404,19 @@
       <c r="D49">
         <v>0</v>
       </c>
-      <c r="E49">
-        <v>0</v>
+      <c r="E49" t="s">
+        <v>102</v>
       </c>
       <c r="F49">
-        <v>-0.3226</v>
+        <v>0.68410000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B50" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -3480,15 +3428,15 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>-0.26989999999999997</v>
+        <v>0.80610000000000004</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -3500,15 +3448,15 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>-0.2586</v>
+        <v>1.4131</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -3516,251 +3464,11 @@
       <c r="D52">
         <v>0</v>
       </c>
-      <c r="E52">
-        <v>0</v>
+      <c r="E52" t="s">
+        <v>102</v>
       </c>
       <c r="F52">
-        <v>-0.25419999999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>158</v>
-      </c>
-      <c r="B53" t="s">
-        <v>153</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53" t="s">
-        <v>116</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>-0.1804</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" t="s">
-        <v>153</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54" t="s">
-        <v>116</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>-0.1711</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>160</v>
-      </c>
-      <c r="B55" t="s">
-        <v>153</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <v>-0.1318</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>161</v>
-      </c>
-      <c r="B56" t="s">
-        <v>153</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>0.2024</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>162</v>
-      </c>
-      <c r="B57" t="s">
-        <v>153</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>0.20849999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>163</v>
-      </c>
-      <c r="B58" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58" t="s">
-        <v>116</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>0.23100000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>164</v>
-      </c>
-      <c r="B59" t="s">
-        <v>153</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>0.3135</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>165</v>
-      </c>
-      <c r="B60" t="s">
-        <v>153</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>0.50170000000000003</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>166</v>
-      </c>
-      <c r="B61" t="s">
-        <v>153</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61" t="s">
-        <v>116</v>
-      </c>
-      <c r="F61">
-        <v>0.6845</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>167</v>
-      </c>
-      <c r="B62" t="s">
-        <v>153</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>0.79100000000000004</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>168</v>
-      </c>
-      <c r="B63" t="s">
-        <v>153</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>0.90290000000000004</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>169</v>
-      </c>
-      <c r="B64" t="s">
-        <v>153</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64" t="s">
-        <v>116</v>
-      </c>
-      <c r="F64">
-        <v>1.2950999999999999</v>
+        <v>1.4298</v>
       </c>
     </row>
   </sheetData>
@@ -3771,434 +3479,443 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
     <col min="3" max="4" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>264</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>-0.37069999999999997</v>
+      </c>
+      <c r="D2">
+        <v>-0.37069999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3">
-        <v>-0.37069999999999997</v>
+        <v>-0.36499999999999999</v>
       </c>
       <c r="D3">
-        <v>-0.37069999999999997</v>
+        <v>-0.36499999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-0.36499999999999999</v>
+        <v>-0.35270000000000001</v>
       </c>
       <c r="D4">
-        <v>-0.36499999999999999</v>
+        <v>-0.35270000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-0.35270000000000001</v>
+        <v>-0.34589999999999999</v>
       </c>
       <c r="D5">
-        <v>-0.35270000000000001</v>
+        <v>-0.34589999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6">
-        <v>-0.34589999999999999</v>
+        <v>-0.3044</v>
       </c>
       <c r="D6">
-        <v>-0.34589999999999999</v>
+        <v>-0.3044</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-0.3044</v>
+        <v>-0.27260000000000001</v>
       </c>
       <c r="D7">
-        <v>-0.3044</v>
+        <v>-0.27260000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-0.27260000000000001</v>
+        <v>-0.25900000000000001</v>
       </c>
       <c r="D8">
-        <v>-0.27260000000000001</v>
+        <v>-0.25900000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9">
-        <v>-0.25900000000000001</v>
+        <v>-0.25769999999999998</v>
       </c>
       <c r="D9">
-        <v>-0.25900000000000001</v>
+        <v>-0.25769999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-0.25769999999999998</v>
+        <v>-0.24179999999999999</v>
       </c>
       <c r="D10">
-        <v>-0.25769999999999998</v>
+        <v>-0.24179999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
         <v>5</v>
       </c>
       <c r="C11">
-        <v>-0.24179999999999999</v>
+        <v>-0.22020000000000001</v>
       </c>
       <c r="D11">
-        <v>-0.24179999999999999</v>
+        <v>-0.22020000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12">
-        <v>-0.22020000000000001</v>
+        <v>0.21329999999999999</v>
       </c>
       <c r="D12">
-        <v>-0.22020000000000001</v>
+        <v>0.21329999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13">
-        <v>0.21329999999999999</v>
+        <v>0.2228</v>
       </c>
       <c r="D13">
-        <v>0.21329999999999999</v>
+        <v>0.2228</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14">
-        <v>0.2228</v>
+        <v>0.24</v>
       </c>
       <c r="D14">
-        <v>0.2228</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15">
-        <v>0.24</v>
+        <v>0.25419999999999998</v>
       </c>
       <c r="D15">
-        <v>0.24</v>
+        <v>0.25419999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16">
-        <v>0.25419999999999998</v>
+        <v>0.29120000000000001</v>
       </c>
       <c r="D16">
-        <v>0.25419999999999998</v>
+        <v>0.29120000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17">
-        <v>0.29120000000000001</v>
+        <v>0.30940000000000001</v>
       </c>
       <c r="D17">
-        <v>0.29120000000000001</v>
+        <v>0.30940000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
       </c>
       <c r="C18">
-        <v>0.30940000000000001</v>
+        <v>0.31780000000000003</v>
       </c>
       <c r="D18">
-        <v>0.30940000000000001</v>
+        <v>0.31780000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
       </c>
       <c r="C19">
-        <v>0.31780000000000003</v>
+        <v>0.32669999999999999</v>
       </c>
       <c r="D19">
-        <v>0.31780000000000003</v>
+        <v>0.32669999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20">
-        <v>0.32669999999999999</v>
+        <v>0.34699999999999998</v>
       </c>
       <c r="D20">
-        <v>0.32669999999999999</v>
+        <v>0.34699999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
       </c>
       <c r="C21">
-        <v>0.34699999999999998</v>
+        <v>0.35110000000000002</v>
       </c>
       <c r="D21">
-        <v>0.34699999999999998</v>
+        <v>0.35110000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22">
-        <v>0.35110000000000002</v>
+        <v>0.36730000000000002</v>
       </c>
       <c r="D22">
-        <v>0.35110000000000002</v>
+        <v>0.36730000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23">
-        <v>0.36730000000000002</v>
+        <v>0.41320000000000001</v>
       </c>
       <c r="D23">
-        <v>0.36730000000000002</v>
+        <v>0.41320000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24">
-        <v>0.41320000000000001</v>
+        <v>0.44440000000000002</v>
       </c>
       <c r="D24">
-        <v>0.41320000000000001</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25">
-        <v>0.44440000000000002</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="D25">
-        <v>0.44440000000000002</v>
+        <v>0.45300000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26">
-        <v>0.45300000000000001</v>
+        <v>0.52170000000000005</v>
       </c>
       <c r="D26">
-        <v>0.45300000000000001</v>
+        <v>0.52170000000000005</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27">
-        <v>0.52170000000000005</v>
+        <v>0.3629</v>
       </c>
       <c r="D27">
-        <v>0.52170000000000005</v>
+        <v>0.70369999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28">
-        <v>0.3629</v>
+        <v>0.28720000000000001</v>
       </c>
       <c r="D28">
-        <v>0.70369999999999999</v>
+        <v>0.80789999999999995</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29">
-        <v>0.28720000000000001</v>
+        <v>1.1549</v>
       </c>
       <c r="D29">
-        <v>0.80789999999999995</v>
+        <v>1.5047999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>183</v>
       </c>
       <c r="C30">
-        <v>1.1549</v>
+        <v>0.2195</v>
       </c>
       <c r="D30">
-        <v>1.5047999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C31">
-        <v>0.2195</v>
+        <v>0.34129999999999999</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -4206,21 +3923,21 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="C32">
-        <v>0.34129999999999999</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>-0.52480000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
         <v>50</v>
@@ -4229,12 +3946,12 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>-0.52480000000000004</v>
+        <v>-0.52010000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
         <v>50</v>
@@ -4243,12 +3960,12 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>-0.52010000000000001</v>
+        <v>-0.51849999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
         <v>50</v>
@@ -4257,12 +3974,12 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>-0.51849999999999996</v>
+        <v>-0.47770000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s">
         <v>50</v>
@@ -4271,12 +3988,12 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>-0.47770000000000001</v>
+        <v>-0.4456</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
         <v>50</v>
@@ -4285,12 +4002,12 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>-0.4456</v>
+        <v>-0.44209999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s">
         <v>50</v>
@@ -4299,12 +4016,12 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>-0.44209999999999999</v>
+        <v>-0.44009999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
         <v>50</v>
@@ -4313,12 +4030,12 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>-0.44009999999999999</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
         <v>50</v>
@@ -4327,12 +4044,12 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>-0.43</v>
+        <v>-0.40960000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
         <v>50</v>
@@ -4341,12 +4058,12 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>-0.40960000000000002</v>
+        <v>-0.3841</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
         <v>50</v>
@@ -4355,12 +4072,12 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>-0.3841</v>
+        <v>-0.36820000000000003</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
@@ -4369,12 +4086,12 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>-0.36820000000000003</v>
+        <v>-0.3569</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="B44" t="s">
         <v>50</v>
@@ -4383,12 +4100,12 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>-0.3569</v>
+        <v>-0.35620000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B45" t="s">
         <v>50</v>
@@ -4397,12 +4114,12 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>-0.35620000000000002</v>
+        <v>-0.35499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B46" t="s">
         <v>50</v>
@@ -4411,12 +4128,12 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>-0.35499999999999998</v>
+        <v>-0.33090000000000003</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
@@ -4425,12 +4142,12 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>-0.33090000000000003</v>
+        <v>-0.32579999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B48" t="s">
         <v>50</v>
@@ -4439,12 +4156,12 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>-0.32579999999999998</v>
+        <v>-0.32290000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="B49" t="s">
         <v>50</v>
@@ -4453,12 +4170,12 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>-0.32290000000000002</v>
+        <v>-0.31369999999999998</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B50" t="s">
         <v>50</v>
@@ -4467,12 +4184,12 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>-0.31369999999999998</v>
+        <v>-0.31280000000000002</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B51" t="s">
         <v>50</v>
@@ -4481,12 +4198,12 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>-0.31280000000000002</v>
+        <v>-0.29060000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B52" t="s">
         <v>50</v>
@@ -4495,12 +4212,12 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>-0.29060000000000002</v>
+        <v>-0.29020000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B53" t="s">
         <v>50</v>
@@ -4509,12 +4226,12 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>-0.29020000000000001</v>
+        <v>-0.2823</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B54" t="s">
         <v>50</v>
@@ -4523,12 +4240,12 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>-0.2823</v>
+        <v>-0.2636</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B55" t="s">
         <v>50</v>
@@ -4537,12 +4254,12 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>-0.2636</v>
+        <v>-0.26219999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B56" t="s">
         <v>50</v>
@@ -4551,12 +4268,12 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>-0.26219999999999999</v>
+        <v>-0.2611</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="B57" t="s">
         <v>50</v>
@@ -4565,12 +4282,12 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>-0.2611</v>
+        <v>-0.25030000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B58" t="s">
         <v>50</v>
@@ -4579,12 +4296,12 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>-0.25030000000000002</v>
+        <v>-0.2492</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="B59" t="s">
         <v>50</v>
@@ -4593,12 +4310,12 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>-0.2492</v>
+        <v>-0.22040000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B60" t="s">
         <v>50</v>
@@ -4607,12 +4324,12 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>-0.22040000000000001</v>
+        <v>-0.21049999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B61" t="s">
         <v>50</v>
@@ -4621,12 +4338,12 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>-0.21049999999999999</v>
+        <v>0.22559999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B62" t="s">
         <v>50</v>
@@ -4635,12 +4352,12 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>0.22559999999999999</v>
+        <v>0.23810000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B63" t="s">
         <v>50</v>
@@ -4649,12 +4366,12 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>0.23810000000000001</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B64" t="s">
         <v>50</v>
@@ -4663,12 +4380,12 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0.2424</v>
+        <v>0.25919999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B65" t="s">
         <v>50</v>
@@ -4677,12 +4394,12 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0.25919999999999999</v>
+        <v>0.28349999999999997</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B66" t="s">
         <v>50</v>
@@ -4691,12 +4408,12 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>0.28349999999999997</v>
+        <v>0.31850000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="B67" t="s">
         <v>50</v>
@@ -4705,12 +4422,12 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0.31850000000000001</v>
+        <v>0.33310000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="B68" t="s">
         <v>50</v>
@@ -4719,12 +4436,12 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0.33310000000000001</v>
+        <v>0.3493</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B69" t="s">
         <v>50</v>
@@ -4733,12 +4450,12 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0.3493</v>
+        <v>0.37769999999999998</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B70" t="s">
         <v>50</v>
@@ -4747,12 +4464,12 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0.37769999999999998</v>
+        <v>0.37809999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s">
         <v>50</v>
@@ -4761,12 +4478,12 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0.37809999999999999</v>
+        <v>0.38300000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B72" t="s">
         <v>50</v>
@@ -4775,12 +4492,12 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0.38300000000000001</v>
+        <v>0.45079999999999998</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="B73" t="s">
         <v>50</v>
@@ -4789,12 +4506,12 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.45079999999999998</v>
+        <v>0.45850000000000002</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="B74" t="s">
         <v>50</v>
@@ -4803,12 +4520,12 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0.45850000000000002</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="B75" t="s">
         <v>50</v>
@@ -4817,12 +4534,12 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0.48</v>
+        <v>0.4919</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B76" t="s">
         <v>50</v>
@@ -4831,12 +4548,12 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0.4919</v>
+        <v>0.50260000000000005</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="B77" t="s">
         <v>50</v>
@@ -4845,12 +4562,12 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0.50260000000000005</v>
+        <v>0.51170000000000004</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="B78" t="s">
         <v>50</v>
@@ -4859,12 +4576,12 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>0.51170000000000004</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="B79" t="s">
         <v>50</v>
@@ -4873,12 +4590,12 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0.5333</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B80" t="s">
         <v>50</v>
@@ -4887,12 +4604,12 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>0.54</v>
+        <v>0.54339999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="B81" t="s">
         <v>50</v>
@@ -4901,12 +4618,12 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.54339999999999999</v>
+        <v>0.54879999999999995</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B82" t="s">
         <v>50</v>
@@ -4915,12 +4632,12 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0.54879999999999995</v>
+        <v>0.55479999999999996</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="B83" t="s">
         <v>50</v>
@@ -4929,12 +4646,12 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>0.55479999999999996</v>
+        <v>0.55610000000000004</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B84" t="s">
         <v>50</v>
@@ -4943,12 +4660,12 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.55610000000000004</v>
+        <v>0.61680000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="B85" t="s">
         <v>50</v>
@@ -4957,12 +4674,12 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>0.61680000000000001</v>
+        <v>0.63449999999999995</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="B86" t="s">
         <v>50</v>
@@ -4971,12 +4688,12 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.63449999999999995</v>
+        <v>0.65620000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="B87" t="s">
         <v>50</v>
@@ -4985,12 +4702,12 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0.65620000000000001</v>
+        <v>0.67130000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="B88" t="s">
         <v>50</v>
@@ -4999,12 +4716,12 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>0.67130000000000001</v>
+        <v>0.68469999999999998</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="B89" t="s">
         <v>50</v>
@@ -5013,12 +4730,12 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0.68469999999999998</v>
+        <v>0.68869999999999998</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B90" t="s">
         <v>50</v>
@@ -5027,12 +4744,12 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.68869999999999998</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B91" t="s">
         <v>50</v>
@@ -5041,12 +4758,12 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.745</v>
+        <v>0.74539999999999995</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="B92" t="s">
         <v>50</v>
@@ -5055,20 +4772,6 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.74539999999999995</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>261</v>
-      </c>
-      <c r="B93" t="s">
-        <v>50</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-      <c r="D93">
         <v>0.80259999999999998</v>
       </c>
     </row>
